--- a/templates/delivery_note_fala.xlsx
+++ b/templates/delivery_note_fala.xlsx
@@ -71,7 +71,7 @@
     <t>{{order_no}}</t>
   </si>
   <si>
-    <t>{{L2_customer}}</t>
+    <t>{{l2_customer}}</t>
   </si>
   <si>
     <t>{{applicant}}</t>
